--- a/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/validation/D3_operational_envelope_diagnostics.xlsx
+++ b/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/validation/D3_operational_envelope_diagnostics.xlsx
@@ -10,14 +10,17 @@
     <sheet name="directional_window_burden" sheetId="1" r:id="rId1"/>
     <sheet name="DO_seasonal_high_tail" sheetId="2" r:id="rId2"/>
     <sheet name="ORP_position_season_envelope" sheetId="3" r:id="rId3"/>
-    <sheet name="DO4_zero_deadband_sensitivity" sheetId="4" r:id="rId4"/>
+    <sheet name="DO4_zero_eq_sensitivity" sheetId="4" r:id="rId4"/>
+    <sheet name="DO4_monthly_zero_stability" sheetId="5" r:id="rId5"/>
+    <sheet name="DO4_parallel_line_diagnostic" sheetId="6" r:id="rId6"/>
+    <sheet name="DO4_upper_candidate" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="121">
   <si>
     <t>sensor_id</t>
   </si>
@@ -43,15 +46,36 @@
     <t>max_soft_high_exceedance</t>
   </si>
   <si>
+    <t>physical_low_window_rate</t>
+  </si>
+  <si>
+    <t>zero_equivalent_window_rate</t>
+  </si>
+  <si>
+    <t>zero_offset_warning_window_rate</t>
+  </si>
+  <si>
+    <t>severe_negative_window_rate</t>
+  </si>
+  <si>
     <t>soft_low</t>
   </si>
   <si>
     <t>soft_high</t>
   </si>
   <si>
+    <t>effective_soft_low</t>
+  </si>
+  <si>
+    <t>zero_equivalence_low</t>
+  </si>
+  <si>
     <t>threshold_scope</t>
   </si>
   <si>
+    <t>soft_sensitivity_anchor</t>
+  </si>
+  <si>
     <t>type</t>
   </si>
   <si>
@@ -112,6 +136,15 @@
     <t>sensor_override</t>
   </si>
   <si>
+    <t>lower</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>center</t>
+  </si>
+  <si>
     <t>DO</t>
   </si>
   <si>
@@ -163,7 +196,7 @@
     <t>winter</t>
   </si>
   <si>
-    <t>diagnostic_pending_temperature_pressure_salinity</t>
+    <t>fixed_8_diagnostic_pending_dynamic_saturation_covariates</t>
   </si>
   <si>
     <t>median</t>
@@ -193,7 +226,7 @@
     <t>diagnostic_only_pending_site_review</t>
   </si>
   <si>
-    <t>zero_deadband_low_mg_L</t>
+    <t>zero_equivalence_low_mg_L</t>
   </si>
   <si>
     <t>n_observed</t>
@@ -202,7 +235,7 @@
     <t>negative_value_rate</t>
   </si>
   <si>
-    <t>soft_low_violation_rate</t>
+    <t>zero_offset_warning_rate</t>
   </si>
   <si>
     <t>minimum_observed</t>
@@ -212,12 +245,153 @@
   </si>
   <si>
     <t>sensitivity_not_final_manufacturer_lock</t>
+  </si>
+  <si>
+    <t>month</t>
+  </si>
+  <si>
+    <t>negative_rate</t>
+  </si>
+  <si>
+    <t>negative_median</t>
+  </si>
+  <si>
+    <t>minimum</t>
+  </si>
+  <si>
+    <t>longest_negative_run_min</t>
+  </si>
+  <si>
+    <t>zero_equivalent_rate</t>
+  </si>
+  <si>
+    <t>severe_negative_rate</t>
+  </si>
+  <si>
+    <t>2025-08</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>2025-11</t>
+  </si>
+  <si>
+    <t>2025-12</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>n_paired</t>
+  </si>
+  <si>
+    <t>DO_1_4_median</t>
+  </si>
+  <si>
+    <t>DO_2_4_median</t>
+  </si>
+  <si>
+    <t>negative_jaccard</t>
+  </si>
+  <si>
+    <t>zero_equivalent_jaccard</t>
+  </si>
+  <si>
+    <t>negative_rate_DO_1_4</t>
+  </si>
+  <si>
+    <t>negative_rate_DO_2_4</t>
+  </si>
+  <si>
+    <t>interpretation</t>
+  </si>
+  <si>
+    <t>parallel_line_diagnostic_not_cross_sensor_scoring</t>
+  </si>
+  <si>
+    <t>split_timestamp</t>
+  </si>
+  <si>
+    <t>calibration_hours</t>
+  </si>
+  <si>
+    <t>validation_hours</t>
+  </si>
+  <si>
+    <t>calibration_median_mg_L</t>
+  </si>
+  <si>
+    <t>calibration_MAD_scale_mg_L</t>
+  </si>
+  <si>
+    <t>calibration_p99_mg_L</t>
+  </si>
+  <si>
+    <t>candidate_upper_mg_L</t>
+  </si>
+  <si>
+    <t>validation_warning_rate</t>
+  </si>
+  <si>
+    <t>validation_p99_mg_L</t>
+  </si>
+  <si>
+    <t>support_passed</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>production_role</t>
+  </si>
+  <si>
+    <t>calibration_filter</t>
+  </si>
+  <si>
+    <t>D1_source_sha256</t>
+  </si>
+  <si>
+    <t>D2_source_sha256</t>
+  </si>
+  <si>
+    <t>validation_candidate_support_passed</t>
+  </si>
+  <si>
+    <t>insufficient_independent_support</t>
+  </si>
+  <si>
+    <t>disabled_not_consumed_by_D3_score</t>
+  </si>
+  <si>
+    <t>D1_total,Q_spike,Q_step,Q_freeze,D2_Strict&gt;=4.5</t>
+  </si>
+  <si>
+    <t>83207ca6f818dd309fe36cdb3adfdc9e569ea540fbca5c4acc0e45e8a321923c</t>
+  </si>
+  <si>
+    <t>ac051d9a24a17523433c63187cf63f0128efb185325a1ea789633f7fc13d04a6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -270,11 +444,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -569,10 +744,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -618,10 +793,31 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B2">
         <v>3072</v>
@@ -645,30 +841,48 @@
         <v>2.369999999999999</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.004231770833333333</v>
       </c>
       <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
         <v>8</v>
       </c>
-      <c r="K2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2">
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T2">
         <v>1</v>
       </c>
-      <c r="N2">
+      <c r="U2">
         <v>1</v>
       </c>
-      <c r="O2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="V2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B3">
         <v>3072</v>
@@ -695,27 +909,45 @@
         <v>0</v>
       </c>
       <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
         <v>8</v>
       </c>
-      <c r="K3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3">
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" t="s">
+        <v>38</v>
+      </c>
+      <c r="S3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T3">
         <v>1</v>
       </c>
-      <c r="N3">
+      <c r="U3">
         <v>2</v>
       </c>
-      <c r="O3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="V3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <v>3072</v>
@@ -742,27 +974,45 @@
         <v>0</v>
       </c>
       <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
         <v>8</v>
       </c>
-      <c r="K4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4">
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" t="s">
+        <v>38</v>
+      </c>
+      <c r="S4" t="s">
+        <v>41</v>
+      </c>
+      <c r="T4">
         <v>1</v>
       </c>
-      <c r="N4">
+      <c r="U4">
         <v>3</v>
       </c>
-      <c r="O4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="V4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <v>3072</v>
@@ -771,45 +1021,63 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>0.0003255208333333333</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>1.359878154917319E-05</v>
+        <v>0</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0.5999999999999996</v>
+        <v>0</v>
       </c>
       <c r="I5">
+        <v>0.962890625</v>
+      </c>
+      <c r="J5">
+        <v>0.962890625</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="O5">
         <v>-0.05</v>
       </c>
-      <c r="J5">
-        <v>8</v>
-      </c>
-      <c r="K5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5">
+      <c r="P5">
+        <v>-0.05</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>37</v>
+      </c>
+      <c r="R5" t="s">
+        <v>39</v>
+      </c>
+      <c r="S5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T5">
         <v>1</v>
       </c>
-      <c r="N5">
+      <c r="U5">
         <v>4</v>
       </c>
-      <c r="O5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="V5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B6">
         <v>3072</v>
@@ -836,27 +1104,45 @@
         <v>0</v>
       </c>
       <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
         <v>8</v>
       </c>
-      <c r="K6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M6">
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S6" t="s">
+        <v>41</v>
+      </c>
+      <c r="T6">
         <v>2</v>
       </c>
-      <c r="N6">
+      <c r="U6">
         <v>1</v>
       </c>
-      <c r="O6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="V6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B7">
         <v>3072</v>
@@ -883,27 +1169,45 @@
         <v>0</v>
       </c>
       <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
         <v>8</v>
       </c>
-      <c r="K7" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7" t="s">
-        <v>31</v>
-      </c>
-      <c r="M7">
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>36</v>
+      </c>
+      <c r="R7" t="s">
+        <v>38</v>
+      </c>
+      <c r="S7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T7">
         <v>2</v>
       </c>
-      <c r="N7">
+      <c r="U7">
         <v>2</v>
       </c>
-      <c r="O7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="V7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B8">
         <v>3072</v>
@@ -930,27 +1234,45 @@
         <v>0</v>
       </c>
       <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
         <v>8</v>
       </c>
-      <c r="K8" t="s">
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>36</v>
+      </c>
+      <c r="R8" t="s">
+        <v>38</v>
+      </c>
+      <c r="S8" t="s">
+        <v>41</v>
+      </c>
+      <c r="T8">
+        <v>2</v>
+      </c>
+      <c r="U8">
+        <v>3</v>
+      </c>
+      <c r="V8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="A9" t="s">
         <v>29</v>
-      </c>
-      <c r="L8" t="s">
-        <v>31</v>
-      </c>
-      <c r="M8">
-        <v>2</v>
-      </c>
-      <c r="N8">
-        <v>3</v>
-      </c>
-      <c r="O8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" t="s">
-        <v>22</v>
       </c>
       <c r="B9">
         <v>3072</v>
@@ -974,30 +1296,48 @@
         <v>0</v>
       </c>
       <c r="I9">
+        <v>0.001627604166666667</v>
+      </c>
+      <c r="J9">
+        <v>0.001627604166666667</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="O9">
         <v>-0.05</v>
       </c>
-      <c r="J9">
-        <v>8</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="P9">
+        <v>-0.05</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>37</v>
+      </c>
+      <c r="R9" t="s">
+        <v>39</v>
+      </c>
+      <c r="S9" t="s">
+        <v>41</v>
+      </c>
+      <c r="T9">
+        <v>2</v>
+      </c>
+      <c r="U9">
+        <v>4</v>
+      </c>
+      <c r="V9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="A10" t="s">
         <v>30</v>
-      </c>
-      <c r="L9" t="s">
-        <v>31</v>
-      </c>
-      <c r="M9">
-        <v>2</v>
-      </c>
-      <c r="N9">
-        <v>4</v>
-      </c>
-      <c r="O9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" t="s">
-        <v>23</v>
       </c>
       <c r="B10">
         <v>3072</v>
@@ -1021,30 +1361,48 @@
         <v>0</v>
       </c>
       <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
         <v>-400</v>
       </c>
-      <c r="J10">
+      <c r="N10">
         <v>200</v>
       </c>
-      <c r="K10" t="s">
-        <v>29</v>
-      </c>
-      <c r="L10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M10">
+      <c r="O10">
+        <v>-400</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>36</v>
+      </c>
+      <c r="R10" t="s">
+        <v>40</v>
+      </c>
+      <c r="S10" t="s">
+        <v>42</v>
+      </c>
+      <c r="T10">
         <v>1</v>
       </c>
-      <c r="N10">
+      <c r="U10">
         <v>1</v>
       </c>
-      <c r="O10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="V10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B11">
         <v>3072</v>
@@ -1068,30 +1426,48 @@
         <v>0</v>
       </c>
       <c r="I11">
+        <v>0.02278645833333333</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
         <v>-400</v>
       </c>
-      <c r="J11">
+      <c r="N11">
         <v>200</v>
       </c>
-      <c r="K11" t="s">
-        <v>29</v>
-      </c>
-      <c r="L11" t="s">
+      <c r="O11">
+        <v>-400</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>36</v>
+      </c>
+      <c r="R11" t="s">
+        <v>40</v>
+      </c>
+      <c r="S11" t="s">
+        <v>42</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>2</v>
+      </c>
+      <c r="V11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="A12" t="s">
         <v>32</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-      <c r="N11">
-        <v>2</v>
-      </c>
-      <c r="O11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12" t="s">
-        <v>25</v>
       </c>
       <c r="B12">
         <v>3072</v>
@@ -1115,30 +1491,48 @@
         <v>0</v>
       </c>
       <c r="I12">
+        <v>0.1848958333333333</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
         <v>-400</v>
       </c>
-      <c r="J12">
+      <c r="N12">
         <v>200</v>
       </c>
-      <c r="K12" t="s">
-        <v>29</v>
-      </c>
-      <c r="L12" t="s">
-        <v>32</v>
-      </c>
-      <c r="M12">
+      <c r="O12">
+        <v>-400</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>36</v>
+      </c>
+      <c r="R12" t="s">
+        <v>40</v>
+      </c>
+      <c r="S12" t="s">
+        <v>42</v>
+      </c>
+      <c r="T12">
         <v>1</v>
       </c>
-      <c r="N12">
+      <c r="U12">
         <v>3</v>
       </c>
-      <c r="O12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="V12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B13">
         <v>3072</v>
@@ -1162,30 +1556,48 @@
         <v>0</v>
       </c>
       <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <v>-400</v>
       </c>
-      <c r="J13">
+      <c r="N13">
         <v>200</v>
       </c>
-      <c r="K13" t="s">
-        <v>29</v>
-      </c>
-      <c r="L13" t="s">
-        <v>32</v>
-      </c>
-      <c r="M13">
+      <c r="O13">
+        <v>-400</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>36</v>
+      </c>
+      <c r="R13" t="s">
+        <v>40</v>
+      </c>
+      <c r="S13" t="s">
+        <v>42</v>
+      </c>
+      <c r="T13">
         <v>2</v>
       </c>
-      <c r="N13">
+      <c r="U13">
         <v>1</v>
       </c>
-      <c r="O13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="V13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B14">
         <v>3072</v>
@@ -1209,30 +1621,48 @@
         <v>0</v>
       </c>
       <c r="I14">
+        <v>0.002604166666666667</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
         <v>-400</v>
       </c>
-      <c r="J14">
+      <c r="N14">
         <v>200</v>
       </c>
-      <c r="K14" t="s">
-        <v>29</v>
-      </c>
-      <c r="L14" t="s">
-        <v>32</v>
-      </c>
-      <c r="M14">
+      <c r="O14">
+        <v>-400</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>36</v>
+      </c>
+      <c r="R14" t="s">
+        <v>40</v>
+      </c>
+      <c r="S14" t="s">
+        <v>42</v>
+      </c>
+      <c r="T14">
         <v>2</v>
       </c>
-      <c r="N14">
+      <c r="U14">
         <v>2</v>
       </c>
-      <c r="O14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="V14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B15">
         <v>3072</v>
@@ -1256,25 +1686,43 @@
         <v>0</v>
       </c>
       <c r="I15">
+        <v>0.7119140625</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
         <v>-400</v>
       </c>
-      <c r="J15">
+      <c r="N15">
         <v>200</v>
       </c>
-      <c r="K15" t="s">
-        <v>29</v>
-      </c>
-      <c r="L15" t="s">
-        <v>32</v>
-      </c>
-      <c r="M15">
+      <c r="O15">
+        <v>-400</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>36</v>
+      </c>
+      <c r="R15" t="s">
+        <v>40</v>
+      </c>
+      <c r="S15" t="s">
+        <v>42</v>
+      </c>
+      <c r="T15">
         <v>2</v>
       </c>
-      <c r="N15">
+      <c r="U15">
         <v>3</v>
       </c>
-      <c r="O15" t="s">
-        <v>37</v>
+      <c r="V15" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1284,7 +1732,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1292,33 +1740,33 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C2">
         <v>44503</v>
@@ -1336,15 +1784,15 @@
         <v>0.000471878300339303</v>
       </c>
       <c r="H2" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C3">
         <v>193609</v>
@@ -1362,15 +1810,15 @@
         <v>0.0002014369166722621</v>
       </c>
       <c r="H3" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C4">
         <v>129022</v>
@@ -1388,15 +1836,15 @@
         <v>0.0002557703337415325</v>
       </c>
       <c r="H4" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C5">
         <v>44504</v>
@@ -1414,15 +1862,15 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C6">
         <v>193610</v>
@@ -1440,15 +1888,15 @@
         <v>0.0003822116626207324</v>
       </c>
       <c r="H6" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C7">
         <v>129022</v>
@@ -1466,15 +1914,15 @@
         <v>9.300739408782998E-05</v>
       </c>
       <c r="H7" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C8">
         <v>44501</v>
@@ -1492,15 +1940,15 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C9">
         <v>193610</v>
@@ -1518,15 +1966,15 @@
         <v>1.549506740354321E-05</v>
       </c>
       <c r="H9" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C10">
         <v>129022</v>
@@ -1544,397 +1992,241 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C11">
-        <v>44503</v>
+        <v>44510</v>
       </c>
       <c r="D11">
-        <v>0.25</v>
+        <v>1.58</v>
       </c>
       <c r="E11">
-        <v>0.48</v>
+        <v>2.57</v>
       </c>
       <c r="F11">
-        <v>0.78</v>
+        <v>4.46</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C12">
-        <v>193597</v>
+        <v>193600</v>
       </c>
       <c r="D12">
-        <v>0.18</v>
+        <v>2.13</v>
       </c>
       <c r="E12">
-        <v>0.46</v>
+        <v>3.48</v>
       </c>
       <c r="F12">
-        <v>8.6</v>
+        <v>10.32</v>
       </c>
       <c r="G12">
-        <v>2.582684649038983E-05</v>
+        <v>0.0003357438016528926</v>
       </c>
       <c r="H12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C13">
-        <v>129021</v>
+        <v>129022</v>
       </c>
       <c r="D13">
-        <v>0.09</v>
+        <v>1.7</v>
       </c>
       <c r="E13">
-        <v>0.28</v>
+        <v>2.247899999999936</v>
       </c>
       <c r="F13">
-        <v>1.07</v>
+        <v>10.31</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>0.0002402691013935608</v>
       </c>
       <c r="H13" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C14">
         <v>44510</v>
       </c>
       <c r="D14">
-        <v>1.58</v>
+        <v>1.97</v>
       </c>
       <c r="E14">
-        <v>2.57</v>
+        <v>2.619099999999962</v>
       </c>
       <c r="F14">
-        <v>4.46</v>
+        <v>3.85</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C15">
-        <v>193600</v>
+        <v>193598</v>
       </c>
       <c r="D15">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="E15">
-        <v>3.48</v>
+        <v>3.65</v>
       </c>
       <c r="F15">
-        <v>10.32</v>
+        <v>6.05</v>
       </c>
       <c r="G15">
-        <v>0.0003357438016528926</v>
+        <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C16">
         <v>129022</v>
       </c>
       <c r="D16">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="E16">
-        <v>2.247899999999936</v>
+        <v>2.79</v>
       </c>
       <c r="F16">
-        <v>10.31</v>
+        <v>3.62</v>
       </c>
       <c r="G16">
-        <v>0.0002402691013935608</v>
+        <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C17">
         <v>44510</v>
       </c>
       <c r="D17">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="E17">
-        <v>2.619099999999962</v>
+        <v>2.05</v>
       </c>
       <c r="F17">
-        <v>3.85</v>
+        <v>2.85</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C18">
-        <v>193598</v>
+        <v>193610</v>
       </c>
       <c r="D18">
-        <v>2.22</v>
+        <v>5.08</v>
       </c>
       <c r="E18">
-        <v>3.65</v>
+        <v>5.54</v>
       </c>
       <c r="F18">
-        <v>6.05</v>
+        <v>10.31</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>0.0006198026961417282</v>
       </c>
       <c r="H18" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C19">
         <v>129022</v>
       </c>
       <c r="D19">
-        <v>2.2</v>
+        <v>5.01</v>
       </c>
       <c r="E19">
-        <v>2.79</v>
+        <v>5.48</v>
       </c>
       <c r="F19">
-        <v>3.62</v>
+        <v>10.31</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>0.0002867727984374758</v>
       </c>
       <c r="H19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20">
-        <v>44510</v>
-      </c>
-      <c r="D20">
-        <v>1.64</v>
-      </c>
-      <c r="E20">
-        <v>2.05</v>
-      </c>
-      <c r="F20">
-        <v>2.85</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21">
-        <v>193610</v>
-      </c>
-      <c r="D21">
-        <v>5.08</v>
-      </c>
-      <c r="E21">
-        <v>5.54</v>
-      </c>
-      <c r="F21">
-        <v>10.31</v>
-      </c>
-      <c r="G21">
-        <v>0.0006198026961417282</v>
-      </c>
-      <c r="H21" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22">
-        <v>129022</v>
-      </c>
-      <c r="D22">
-        <v>5.01</v>
-      </c>
-      <c r="E22">
-        <v>5.48</v>
-      </c>
-      <c r="F22">
-        <v>10.31</v>
-      </c>
-      <c r="G22">
-        <v>0.0002867727984374758</v>
-      </c>
-      <c r="H22" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23">
-        <v>44510</v>
-      </c>
-      <c r="D23">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E23">
-        <v>1.02</v>
-      </c>
-      <c r="F23">
-        <v>1.95</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24">
-        <v>193598</v>
-      </c>
-      <c r="D24">
-        <v>0.98</v>
-      </c>
-      <c r="E24">
-        <v>2.32</v>
-      </c>
-      <c r="F24">
-        <v>5.32</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25">
-        <v>129022</v>
-      </c>
-      <c r="D25">
-        <v>0.45</v>
-      </c>
-      <c r="E25">
-        <v>2.4</v>
-      </c>
-      <c r="F25">
-        <v>4.14</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1944,7 +2236,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -1952,78 +2244,78 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E2">
-        <v>44505</v>
+        <v>44503</v>
       </c>
       <c r="F2">
-        <v>-223.03</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>26.62749600000001</v>
+        <v>0.014826</v>
       </c>
       <c r="H2">
-        <v>-302.9124880000001</v>
+        <v>-0.044478</v>
       </c>
       <c r="I2">
-        <v>-143.1475119999999</v>
+        <v>0.044478</v>
       </c>
       <c r="J2">
-        <v>-264.2684</v>
+        <v>-0.02</v>
       </c>
       <c r="K2">
-        <v>-153.7316</v>
+        <v>0.48</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -2032,42 +2324,42 @@
         <v>0</v>
       </c>
       <c r="N2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E3">
-        <v>193615</v>
+        <v>193597</v>
       </c>
       <c r="F3">
-        <v>-199.93</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>66.86525999999999</v>
+        <v>0.014826</v>
       </c>
       <c r="H3">
-        <v>-400.52578</v>
+        <v>-0.044478</v>
       </c>
       <c r="I3">
-        <v>0.6657799999999838</v>
+        <v>0.044478</v>
       </c>
       <c r="J3">
-        <v>-303.2172</v>
+        <v>-0.02</v>
       </c>
       <c r="K3">
-        <v>-61.60280000000028</v>
+        <v>0.46</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -2076,42 +2368,42 @@
         <v>0</v>
       </c>
       <c r="N3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E4">
-        <v>129022</v>
+        <v>129021</v>
       </c>
       <c r="F4">
-        <v>-241.825</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>26.32356299999999</v>
+        <v>0.014826</v>
       </c>
       <c r="H4">
-        <v>-320.795689</v>
+        <v>-0.044478</v>
       </c>
       <c r="I4">
-        <v>-162.854311</v>
+        <v>0.044478</v>
       </c>
       <c r="J4">
-        <v>-288.8779</v>
+        <v>-0.02</v>
       </c>
       <c r="K4">
-        <v>-134.97</v>
+        <v>0.28</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -2120,42 +2412,42 @@
         <v>0</v>
       </c>
       <c r="N4" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E5">
-        <v>44504</v>
+        <v>44510</v>
       </c>
       <c r="F5">
-        <v>-213.2</v>
+        <v>0.13</v>
       </c>
       <c r="G5">
-        <v>42.80266200000001</v>
+        <v>0.133434</v>
       </c>
       <c r="H5">
-        <v>-341.607986</v>
+        <v>-0.270302</v>
       </c>
       <c r="I5">
-        <v>-84.79201399999997</v>
+        <v>0.5303020000000001</v>
       </c>
       <c r="J5">
-        <v>-271.2494</v>
+        <v>0.01</v>
       </c>
       <c r="K5">
-        <v>-108.9014999999999</v>
+        <v>1.02</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -2164,262 +2456,262 @@
         <v>0</v>
       </c>
       <c r="N5" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E6">
-        <v>193611</v>
+        <v>193598</v>
       </c>
       <c r="F6">
-        <v>-147.97</v>
+        <v>0.15</v>
       </c>
       <c r="G6">
-        <v>66.82078199999998</v>
+        <v>0.14826</v>
       </c>
       <c r="H6">
-        <v>-348.4323459999999</v>
+        <v>-0.2947799999999999</v>
       </c>
       <c r="I6">
-        <v>52.49234599999994</v>
+        <v>0.59478</v>
       </c>
       <c r="J6">
-        <v>-396.768</v>
+        <v>0.02</v>
       </c>
       <c r="K6">
-        <v>-42.67</v>
+        <v>2.32</v>
       </c>
       <c r="L6">
-        <v>0.006791969464544886</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E7">
         <v>129022</v>
       </c>
       <c r="F7">
-        <v>-172.23</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G7">
-        <v>67.13212799999998</v>
+        <v>0.029652</v>
       </c>
       <c r="H7">
-        <v>-373.6263839999999</v>
+        <v>-0.018956</v>
       </c>
       <c r="I7">
-        <v>29.16638399999997</v>
+        <v>0.158956</v>
       </c>
       <c r="J7">
-        <v>-404.93</v>
+        <v>0.03</v>
       </c>
       <c r="K7">
-        <v>-88.73</v>
+        <v>2.4</v>
       </c>
       <c r="L7">
-        <v>0.01989583171862163</v>
+        <v>0</v>
       </c>
       <c r="M7">
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E8">
-        <v>44504</v>
+        <v>44505</v>
       </c>
       <c r="F8">
-        <v>-265.2</v>
+        <v>-223.03</v>
       </c>
       <c r="G8">
-        <v>98.44464000000001</v>
+        <v>26.62749600000001</v>
       </c>
       <c r="H8">
-        <v>-560.5339200000001</v>
+        <v>-302.9124880000001</v>
       </c>
       <c r="I8">
-        <v>30.13392000000005</v>
+        <v>-143.1475119999999</v>
       </c>
       <c r="J8">
-        <v>-487.1688</v>
+        <v>-264.2684</v>
       </c>
       <c r="K8">
-        <v>-95.8</v>
+        <v>-153.7316</v>
       </c>
       <c r="L8">
-        <v>0.1310668703936725</v>
+        <v>0</v>
       </c>
       <c r="M8">
         <v>0</v>
       </c>
       <c r="N8" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E9">
-        <v>193612</v>
+        <v>193615</v>
       </c>
       <c r="F9">
-        <v>-147.83</v>
+        <v>-199.93</v>
       </c>
       <c r="G9">
-        <v>163.723518</v>
+        <v>66.86525999999999</v>
       </c>
       <c r="H9">
-        <v>-639.0005540000001</v>
+        <v>-400.52578</v>
       </c>
       <c r="I9">
-        <v>343.340554</v>
+        <v>0.6657799999999838</v>
       </c>
       <c r="J9">
-        <v>-499.5</v>
+        <v>-303.2172</v>
       </c>
       <c r="K9">
-        <v>23.95</v>
+        <v>-61.60280000000028</v>
       </c>
       <c r="L9">
-        <v>0.1573404541040845</v>
+        <v>0</v>
       </c>
       <c r="M9">
         <v>0</v>
       </c>
       <c r="N9" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E10">
         <v>129022</v>
       </c>
       <c r="F10">
-        <v>-194.07</v>
+        <v>-241.825</v>
       </c>
       <c r="G10">
-        <v>66.27222000000002</v>
+        <v>26.32356299999999</v>
       </c>
       <c r="H10">
-        <v>-392.8866600000001</v>
+        <v>-320.795689</v>
       </c>
       <c r="I10">
-        <v>4.746660000000077</v>
+        <v>-162.854311</v>
       </c>
       <c r="J10">
-        <v>-491.8779</v>
+        <v>-288.8779</v>
       </c>
       <c r="K10">
-        <v>-19.68420000000013</v>
+        <v>-134.97</v>
       </c>
       <c r="L10">
-        <v>0.1546635457518873</v>
+        <v>0</v>
       </c>
       <c r="M10">
         <v>0</v>
       </c>
       <c r="N10" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E11">
-        <v>44509</v>
+        <v>44504</v>
       </c>
       <c r="F11">
-        <v>-247.88</v>
+        <v>-213.2</v>
       </c>
       <c r="G11">
-        <v>23.84020799999998</v>
+        <v>42.80266200000001</v>
       </c>
       <c r="H11">
-        <v>-319.4006239999999</v>
+        <v>-341.607986</v>
       </c>
       <c r="I11">
-        <v>-176.3593760000001</v>
+        <v>-84.79201399999997</v>
       </c>
       <c r="J11">
-        <v>-284.1484</v>
+        <v>-271.2494</v>
       </c>
       <c r="K11">
-        <v>-159.8080000000002</v>
+        <v>-108.9014999999999</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -2428,359 +2720,623 @@
         <v>0</v>
       </c>
       <c r="N11" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E12">
-        <v>193607</v>
+        <v>193611</v>
       </c>
       <c r="F12">
-        <v>-198.4</v>
+        <v>-147.97</v>
       </c>
       <c r="G12">
-        <v>53.96664000000001</v>
+        <v>66.82078199999998</v>
       </c>
       <c r="H12">
-        <v>-360.29992</v>
+        <v>-348.4323459999999</v>
       </c>
       <c r="I12">
-        <v>-36.50008</v>
+        <v>52.49234599999994</v>
       </c>
       <c r="J12">
-        <v>-380.63</v>
+        <v>-396.768</v>
       </c>
       <c r="K12">
-        <v>-5.770599999999976</v>
+        <v>-42.67</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>0.006791969464544886</v>
       </c>
       <c r="M12">
         <v>0</v>
       </c>
       <c r="N12" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E13">
         <v>129022</v>
       </c>
       <c r="F13">
-        <v>-214.3</v>
+        <v>-172.23</v>
       </c>
       <c r="G13">
-        <v>31.920378</v>
+        <v>67.13212799999998</v>
       </c>
       <c r="H13">
-        <v>-310.061134</v>
+        <v>-373.6263839999999</v>
       </c>
       <c r="I13">
-        <v>-118.538866</v>
+        <v>29.16638399999997</v>
       </c>
       <c r="J13">
-        <v>-261.4</v>
+        <v>-404.93</v>
       </c>
       <c r="K13">
-        <v>-91.65420000000013</v>
+        <v>-88.73</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>0.01989583171862163</v>
       </c>
       <c r="M13">
         <v>0</v>
       </c>
       <c r="N13" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E14">
-        <v>44508</v>
+        <v>44504</v>
       </c>
       <c r="F14">
-        <v>-336.2</v>
+        <v>-265.2</v>
       </c>
       <c r="G14">
-        <v>29.05895999999995</v>
+        <v>98.44464000000001</v>
       </c>
       <c r="H14">
-        <v>-423.3768799999998</v>
+        <v>-560.5339200000001</v>
       </c>
       <c r="I14">
-        <v>-249.0231200000001</v>
+        <v>30.13392000000005</v>
       </c>
       <c r="J14">
-        <v>-371.1986</v>
+        <v>-487.1688</v>
       </c>
       <c r="K14">
-        <v>-285.4207</v>
+        <v>-95.8</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>0.1310668703936725</v>
       </c>
       <c r="M14">
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E15">
-        <v>193607</v>
+        <v>193612</v>
       </c>
       <c r="F15">
-        <v>-280.82</v>
+        <v>-147.83</v>
       </c>
       <c r="G15">
-        <v>25.87136999999998</v>
+        <v>163.723518</v>
       </c>
       <c r="H15">
-        <v>-358.4341099999999</v>
+        <v>-639.0005540000001</v>
       </c>
       <c r="I15">
-        <v>-203.2058900000001</v>
+        <v>343.340554</v>
       </c>
       <c r="J15">
-        <v>-391.65</v>
+        <v>-499.5</v>
       </c>
       <c r="K15">
-        <v>-224</v>
+        <v>23.95</v>
       </c>
       <c r="L15">
-        <v>0.001296440727866245</v>
+        <v>0.1573404541040845</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
       <c r="N15" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E16">
         <v>129022</v>
       </c>
       <c r="F16">
-        <v>-283.2</v>
+        <v>-194.07</v>
       </c>
       <c r="G16">
-        <v>29.20721999999998</v>
+        <v>66.27222000000002</v>
       </c>
       <c r="H16">
-        <v>-370.82166</v>
+        <v>-392.8866600000001</v>
       </c>
       <c r="I16">
-        <v>-195.57834</v>
+        <v>4.746660000000077</v>
       </c>
       <c r="J16">
-        <v>-385.67</v>
+        <v>-491.8779</v>
       </c>
       <c r="K16">
-        <v>-244.58</v>
+        <v>-19.68420000000013</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>0.1546635457518873</v>
       </c>
       <c r="M16">
         <v>0</v>
       </c>
       <c r="N16" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E17">
-        <v>44510</v>
+        <v>44509</v>
       </c>
       <c r="F17">
-        <v>-373.93</v>
+        <v>-247.88</v>
       </c>
       <c r="G17">
-        <v>138.652752</v>
+        <v>23.84020799999998</v>
       </c>
       <c r="H17">
-        <v>-789.888256</v>
+        <v>-319.4006239999999</v>
       </c>
       <c r="I17">
-        <v>42.02825599999989</v>
+        <v>-176.3593760000001</v>
       </c>
       <c r="J17">
-        <v>-481.55</v>
+        <v>-284.1484</v>
       </c>
       <c r="K17">
-        <v>-3.520900000000038</v>
+        <v>-159.8080000000002</v>
       </c>
       <c r="L17">
-        <v>0.4344866322174792</v>
+        <v>0</v>
       </c>
       <c r="M17">
         <v>0</v>
       </c>
       <c r="N17" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E18">
-        <v>193608</v>
+        <v>193607</v>
       </c>
       <c r="F18">
-        <v>-386.525</v>
+        <v>-198.4</v>
       </c>
       <c r="G18">
-        <v>115.798473</v>
+        <v>53.96664000000001</v>
       </c>
       <c r="H18">
-        <v>-733.920419</v>
+        <v>-360.29992</v>
       </c>
       <c r="I18">
-        <v>-39.12958099999992</v>
+        <v>-36.50008</v>
       </c>
       <c r="J18">
-        <v>-478.3</v>
+        <v>-380.63</v>
       </c>
       <c r="K18">
-        <v>38.5</v>
+        <v>-5.770599999999976</v>
       </c>
       <c r="L18">
-        <v>0.4748874013470518</v>
+        <v>0</v>
       </c>
       <c r="M18">
         <v>0</v>
       </c>
       <c r="N18" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E19">
         <v>129022</v>
       </c>
       <c r="F19">
+        <v>-214.3</v>
+      </c>
+      <c r="G19">
+        <v>31.920378</v>
+      </c>
+      <c r="H19">
+        <v>-310.061134</v>
+      </c>
+      <c r="I19">
+        <v>-118.538866</v>
+      </c>
+      <c r="J19">
+        <v>-261.4</v>
+      </c>
+      <c r="K19">
+        <v>-91.65420000000013</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20">
+        <v>44508</v>
+      </c>
+      <c r="F20">
+        <v>-336.2</v>
+      </c>
+      <c r="G20">
+        <v>29.05895999999995</v>
+      </c>
+      <c r="H20">
+        <v>-423.3768799999998</v>
+      </c>
+      <c r="I20">
+        <v>-249.0231200000001</v>
+      </c>
+      <c r="J20">
+        <v>-371.1986</v>
+      </c>
+      <c r="K20">
+        <v>-285.4207</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21">
+        <v>193607</v>
+      </c>
+      <c r="F21">
+        <v>-280.82</v>
+      </c>
+      <c r="G21">
+        <v>25.87136999999998</v>
+      </c>
+      <c r="H21">
+        <v>-358.4341099999999</v>
+      </c>
+      <c r="I21">
+        <v>-203.2058900000001</v>
+      </c>
+      <c r="J21">
+        <v>-391.65</v>
+      </c>
+      <c r="K21">
+        <v>-224</v>
+      </c>
+      <c r="L21">
+        <v>0.001296440727866245</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>57</v>
+      </c>
+      <c r="E22">
+        <v>129022</v>
+      </c>
+      <c r="F22">
+        <v>-283.2</v>
+      </c>
+      <c r="G22">
+        <v>29.20721999999998</v>
+      </c>
+      <c r="H22">
+        <v>-370.82166</v>
+      </c>
+      <c r="I22">
+        <v>-195.57834</v>
+      </c>
+      <c r="J22">
+        <v>-385.67</v>
+      </c>
+      <c r="K22">
+        <v>-244.58</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+      <c r="D23" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23">
+        <v>44510</v>
+      </c>
+      <c r="F23">
+        <v>-373.93</v>
+      </c>
+      <c r="G23">
+        <v>138.652752</v>
+      </c>
+      <c r="H23">
+        <v>-789.888256</v>
+      </c>
+      <c r="I23">
+        <v>42.02825599999989</v>
+      </c>
+      <c r="J23">
+        <v>-481.55</v>
+      </c>
+      <c r="K23">
+        <v>-3.520900000000038</v>
+      </c>
+      <c r="L23">
+        <v>0.4344866322174792</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24">
+        <v>193608</v>
+      </c>
+      <c r="F24">
+        <v>-386.525</v>
+      </c>
+      <c r="G24">
+        <v>115.798473</v>
+      </c>
+      <c r="H24">
+        <v>-733.920419</v>
+      </c>
+      <c r="I24">
+        <v>-39.12958099999992</v>
+      </c>
+      <c r="J24">
+        <v>-478.3</v>
+      </c>
+      <c r="K24">
+        <v>38.5</v>
+      </c>
+      <c r="L24">
+        <v>0.4748874013470518</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
+      </c>
+      <c r="D25" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25">
+        <v>129022</v>
+      </c>
+      <c r="F25">
         <v>-449.6</v>
       </c>
-      <c r="G19">
+      <c r="G25">
         <v>6.968220000000067</v>
       </c>
-      <c r="H19">
+      <c r="H25">
         <v>-470.5046600000002</v>
       </c>
-      <c r="I19">
+      <c r="I25">
         <v>-428.6953399999998</v>
       </c>
-      <c r="J19">
+      <c r="J25">
         <v>-460.3958</v>
       </c>
-      <c r="K19">
+      <c r="K25">
         <v>-218.6063000000002</v>
       </c>
-      <c r="L19">
+      <c r="L25">
         <v>0.8886003937313016</v>
       </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19" t="s">
-        <v>57</v>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -2798,27 +3354,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2836,12 +3392,12 @@
         <v>-0.03</v>
       </c>
       <c r="G2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B3">
         <v>-0.03</v>
@@ -2859,12 +3415,12 @@
         <v>-0.03</v>
       </c>
       <c r="G3" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>-0.05</v>
@@ -2882,12 +3438,12 @@
         <v>-0.03</v>
       </c>
       <c r="G4" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <v>-0.1</v>
@@ -2905,12 +3461,12 @@
         <v>-0.03</v>
       </c>
       <c r="G5" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2928,12 +3484,12 @@
         <v>-0.01</v>
       </c>
       <c r="G6" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B7">
         <v>-0.03</v>
@@ -2951,12 +3507,12 @@
         <v>-0.01</v>
       </c>
       <c r="G7" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B8">
         <v>-0.05</v>
@@ -2974,12 +3530,12 @@
         <v>-0.01</v>
       </c>
       <c r="G8" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B9">
         <v>-0.1</v>
@@ -2997,7 +3553,1118 @@
         <v>-0.01</v>
       </c>
       <c r="G9" t="s">
-        <v>64</v>
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2">
+        <v>44503</v>
+      </c>
+      <c r="D2">
+        <v>0.3182257375907242</v>
+      </c>
+      <c r="E2">
+        <v>-0.01</v>
+      </c>
+      <c r="F2">
+        <v>-0.02</v>
+      </c>
+      <c r="G2">
+        <v>-0.03</v>
+      </c>
+      <c r="H2">
+        <v>11</v>
+      </c>
+      <c r="I2">
+        <v>0.3182257375907242</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3">
+        <v>42834</v>
+      </c>
+      <c r="D3">
+        <v>0.3292477938086567</v>
+      </c>
+      <c r="E3">
+        <v>-0.01</v>
+      </c>
+      <c r="F3">
+        <v>-0.02</v>
+      </c>
+      <c r="G3">
+        <v>-0.03</v>
+      </c>
+      <c r="H3">
+        <v>12</v>
+      </c>
+      <c r="I3">
+        <v>0.3292477938086567</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4">
+        <v>44625</v>
+      </c>
+      <c r="D4">
+        <v>0.2186666666666667</v>
+      </c>
+      <c r="E4">
+        <v>-0.01</v>
+      </c>
+      <c r="F4">
+        <v>-0.02</v>
+      </c>
+      <c r="G4">
+        <v>-0.03</v>
+      </c>
+      <c r="H4">
+        <v>8</v>
+      </c>
+      <c r="I4">
+        <v>0.2186666666666667</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5">
+        <v>43180</v>
+      </c>
+      <c r="D5">
+        <v>0.2064844835572024</v>
+      </c>
+      <c r="E5">
+        <v>-0.01</v>
+      </c>
+      <c r="F5">
+        <v>-0.02</v>
+      </c>
+      <c r="G5">
+        <v>-0.03</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>0.2064844835572024</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6">
+        <v>44640</v>
+      </c>
+      <c r="D6">
+        <v>0.3059811827956989</v>
+      </c>
+      <c r="E6">
+        <v>-0.01</v>
+      </c>
+      <c r="F6">
+        <v>-0.02</v>
+      </c>
+      <c r="G6">
+        <v>-0.03</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>0.3059811827956989</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7">
+        <v>44061</v>
+      </c>
+      <c r="D7">
+        <v>0.2220330904881868</v>
+      </c>
+      <c r="E7">
+        <v>-0.01</v>
+      </c>
+      <c r="F7">
+        <v>-0.02</v>
+      </c>
+      <c r="G7">
+        <v>-0.03</v>
+      </c>
+      <c r="H7">
+        <v>9</v>
+      </c>
+      <c r="I7">
+        <v>0.2220330904881868</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8">
+        <v>40320</v>
+      </c>
+      <c r="D8">
+        <v>0.2364831349206349</v>
+      </c>
+      <c r="E8">
+        <v>-0.01</v>
+      </c>
+      <c r="F8">
+        <v>-0.02</v>
+      </c>
+      <c r="G8">
+        <v>-0.03</v>
+      </c>
+      <c r="H8">
+        <v>9</v>
+      </c>
+      <c r="I8">
+        <v>0.2364831349206349</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9">
+        <v>44640</v>
+      </c>
+      <c r="D9">
+        <v>0.1788306451612903</v>
+      </c>
+      <c r="E9">
+        <v>-0.01</v>
+      </c>
+      <c r="F9">
+        <v>-0.01</v>
+      </c>
+      <c r="G9">
+        <v>-0.03</v>
+      </c>
+      <c r="H9">
+        <v>8</v>
+      </c>
+      <c r="I9">
+        <v>0.1788306451612903</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10">
+        <v>18318</v>
+      </c>
+      <c r="D10">
+        <v>0.2748116606616443</v>
+      </c>
+      <c r="E10">
+        <v>-0.01</v>
+      </c>
+      <c r="F10">
+        <v>-0.02</v>
+      </c>
+      <c r="G10">
+        <v>-0.03</v>
+      </c>
+      <c r="H10">
+        <v>8</v>
+      </c>
+      <c r="I10">
+        <v>0.2748116606616443</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11">
+        <v>44510</v>
+      </c>
+      <c r="D11">
+        <v>0.0002022017524151876</v>
+      </c>
+      <c r="E11">
+        <v>-0.01</v>
+      </c>
+      <c r="F11">
+        <v>0.01</v>
+      </c>
+      <c r="G11">
+        <v>-0.01</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11">
+        <v>0.0002022017524151876</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12">
+        <v>42832</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0.01</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13">
+        <v>44628</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0.02</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14">
+        <v>43180</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0.04</v>
+      </c>
+      <c r="G14">
+        <v>0.02</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15">
+        <v>44640</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0.03</v>
+      </c>
+      <c r="G15">
+        <v>0.02</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16">
+        <v>44062</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0.04</v>
+      </c>
+      <c r="G16">
+        <v>0.02</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17">
+        <v>40320</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0.04</v>
+      </c>
+      <c r="G17">
+        <v>0.02</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18">
+        <v>44640</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19">
+        <v>18318</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0.03</v>
+      </c>
+      <c r="G19">
+        <v>0.02</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2">
+        <v>44498</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0.13</v>
+      </c>
+      <c r="E2">
+        <v>0.0002117746717492588</v>
+      </c>
+      <c r="F2">
+        <v>0.0002117746717492588</v>
+      </c>
+      <c r="G2">
+        <v>0.3182165490583846</v>
+      </c>
+      <c r="H2">
+        <v>0.0002022562811811767</v>
+      </c>
+      <c r="I2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3">
+        <v>42830</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0.3</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0.3292785430772823</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4">
+        <v>44617</v>
+      </c>
+      <c r="C4">
+        <v>0.01</v>
+      </c>
+      <c r="D4">
+        <v>0.16</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0.2186610484792792</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5">
+        <v>43179</v>
+      </c>
+      <c r="C5">
+        <v>0.01</v>
+      </c>
+      <c r="D5">
+        <v>0.21</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0.2064892656152296</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6">
+        <v>44640</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0.06</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0.3059811827956989</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7">
+        <v>44061</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0.2220330904881868</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8">
+        <v>40320</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0.08</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0.2364831349206349</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9">
+        <v>44640</v>
+      </c>
+      <c r="C9">
+        <v>0.01</v>
+      </c>
+      <c r="D9">
+        <v>0.09</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0.1788306451612903</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10">
+        <v>18318</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0.05</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0.2748116606616443</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="2">
+        <v>46049.19951388889</v>
+      </c>
+      <c r="C2">
+        <v>2727</v>
+      </c>
+      <c r="D2">
+        <v>1329</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.1086999999999989</v>
+      </c>
+      <c r="H2">
+        <v>0.1086999999999989</v>
+      </c>
+      <c r="I2">
+        <v>0.002257336343115124</v>
+      </c>
+      <c r="J2">
+        <v>0.04720000000000028</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>115</v>
+      </c>
+      <c r="M2" t="s">
+        <v>117</v>
+      </c>
+      <c r="N2" t="s">
+        <v>118</v>
+      </c>
+      <c r="O2" t="s">
+        <v>119</v>
+      </c>
+      <c r="P2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="2">
+        <v>46049.19951388889</v>
+      </c>
+      <c r="C3">
+        <v>98</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>0.3075</v>
+      </c>
+      <c r="F3">
+        <v>0.1816185</v>
+      </c>
+      <c r="G3">
+        <v>1.058750000000002</v>
+      </c>
+      <c r="H3">
+        <v>1.058750000000002</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.6564</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="s">
+        <v>116</v>
+      </c>
+      <c r="M3" t="s">
+        <v>117</v>
+      </c>
+      <c r="N3" t="s">
+        <v>118</v>
+      </c>
+      <c r="O3" t="s">
+        <v>119</v>
+      </c>
+      <c r="P3" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/validation/D3_operational_envelope_diagnostics.xlsx
+++ b/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/validation/D3_operational_envelope_diagnostics.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="directional_window_burden" sheetId="1" r:id="rId1"/>
-    <sheet name="DO_seasonal_high_tail" sheetId="2" r:id="rId2"/>
+    <sheet name="DO_seasonal_raw_distribution" sheetId="2" r:id="rId2"/>
     <sheet name="ORP_position_season_envelope" sheetId="3" r:id="rId3"/>
     <sheet name="DO4_zero_eq_sensitivity" sheetId="4" r:id="rId4"/>
     <sheet name="DO4_monthly_zero_stability" sheetId="5" r:id="rId5"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="121">
   <si>
     <t>sensor_id</t>
   </si>
@@ -130,12 +130,15 @@
     <t>ORP_2_3</t>
   </si>
   <si>
+    <t>temperature_conditioned_position_template</t>
+  </si>
+  <si>
+    <t>sensor_override</t>
+  </si>
+  <si>
     <t>sensor_type</t>
   </si>
   <si>
-    <t>sensor_override</t>
-  </si>
-  <si>
     <t>lower</t>
   </si>
   <si>
@@ -181,10 +184,7 @@
     <t>maximum</t>
   </si>
   <si>
-    <t>above_8_rate</t>
-  </si>
-  <si>
-    <t>upper_bound_role</t>
+    <t>distribution_role</t>
   </si>
   <si>
     <t>summer</t>
@@ -196,7 +196,7 @@
     <t>winter</t>
   </si>
   <si>
-    <t>fixed_8_diagnostic_pending_dynamic_saturation_covariates</t>
+    <t>raw_context_only_temperature_envelope_audited_separately</t>
   </si>
   <si>
     <t>median</t>
@@ -826,19 +826,19 @@
         <v>0.004231770833333333</v>
       </c>
       <c r="D2">
-        <v>0.001953125</v>
+        <v>0.02571614583333333</v>
       </c>
       <c r="E2">
         <v>9.156512909776618E-05</v>
       </c>
       <c r="F2">
-        <v>0.0002529373368146214</v>
+        <v>0.008047758920800696</v>
       </c>
       <c r="G2">
         <v>0.02</v>
       </c>
       <c r="H2">
-        <v>2.369999999999999</v>
+        <v>7.881522987720899</v>
       </c>
       <c r="I2">
         <v>0.004231770833333333</v>
@@ -855,9 +855,6 @@
       <c r="M2">
         <v>0</v>
       </c>
-      <c r="N2">
-        <v>8</v>
-      </c>
       <c r="O2">
         <v>0</v>
       </c>
@@ -865,10 +862,10 @@
         <v>36</v>
       </c>
       <c r="R2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T2">
         <v>1</v>
@@ -877,7 +874,7 @@
         <v>1</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -891,19 +888,19 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>0.001627604166666667</v>
+        <v>0.0615234375</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.0002338990426457789</v>
+        <v>0.01225794168842472</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>2.31</v>
+        <v>7.277511266220876</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -919,9 +916,6 @@
       </c>
       <c r="M3">
         <v>0</v>
-      </c>
-      <c r="N3">
-        <v>8</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -930,10 +924,10 @@
         <v>36</v>
       </c>
       <c r="R3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T3">
         <v>1</v>
@@ -942,7 +936,7 @@
         <v>2</v>
       </c>
       <c r="V3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -956,19 +950,19 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>0.0003255208333333333</v>
+        <v>0.003255208333333333</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>8.159268929503916E-06</v>
+        <v>0.0009818320278503045</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0.5099999999999998</v>
+        <v>4.379834524927852</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -984,9 +978,6 @@
       </c>
       <c r="M4">
         <v>0</v>
-      </c>
-      <c r="N4">
-        <v>8</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -995,10 +986,10 @@
         <v>36</v>
       </c>
       <c r="R4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T4">
         <v>1</v>
@@ -1007,7 +998,7 @@
         <v>3</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -1032,9 +1023,6 @@
       <c r="G5">
         <v>0</v>
       </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
       <c r="I5">
         <v>0.962890625</v>
       </c>
@@ -1060,10 +1048,10 @@
         <v>37</v>
       </c>
       <c r="R5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T5">
         <v>1</v>
@@ -1072,7 +1060,7 @@
         <v>4</v>
       </c>
       <c r="V5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1086,19 +1074,19 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0.003580729166666667</v>
+        <v>0.04720052083333334</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.0002610966057441253</v>
+        <v>0.01921030161411823</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>2.32</v>
+        <v>7.634317837507574</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1114,9 +1102,6 @@
       </c>
       <c r="M6">
         <v>0</v>
-      </c>
-      <c r="N6">
-        <v>8</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1125,10 +1110,10 @@
         <v>36</v>
       </c>
       <c r="R6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T6">
         <v>2</v>
@@ -1137,7 +1122,7 @@
         <v>1</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1151,19 +1136,19 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>0.03776041666666666</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>0.01685515263546672</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2.8541182515103</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1179,9 +1164,6 @@
       </c>
       <c r="M7">
         <v>0</v>
-      </c>
-      <c r="N7">
-        <v>8</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1190,10 +1172,10 @@
         <v>36</v>
       </c>
       <c r="R7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T7">
         <v>2</v>
@@ -1202,7 +1184,7 @@
         <v>2</v>
       </c>
       <c r="V7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1216,19 +1198,19 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0.004557291666666667</v>
+        <v>0.5335286458333334</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0.0004270017406440383</v>
+        <v>0.08725617790361966</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>2.31</v>
+        <v>5.724192996097323</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1244,9 +1226,6 @@
       </c>
       <c r="M8">
         <v>0</v>
-      </c>
-      <c r="N8">
-        <v>8</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -1255,10 +1234,10 @@
         <v>36</v>
       </c>
       <c r="R8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T8">
         <v>2</v>
@@ -1267,7 +1246,7 @@
         <v>3</v>
       </c>
       <c r="V8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1292,9 +1271,6 @@
       <c r="G9">
         <v>0</v>
       </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
       <c r="I9">
         <v>0.001627604166666667</v>
       </c>
@@ -1320,10 +1296,10 @@
         <v>37</v>
       </c>
       <c r="R9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T9">
         <v>2</v>
@@ -1332,7 +1308,7 @@
         <v>4</v>
       </c>
       <c r="V9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1382,13 +1358,13 @@
         <v>-400</v>
       </c>
       <c r="Q10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T10">
         <v>1</v>
@@ -1397,7 +1373,7 @@
         <v>1</v>
       </c>
       <c r="V10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1447,13 +1423,13 @@
         <v>-400</v>
       </c>
       <c r="Q11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T11">
         <v>1</v>
@@ -1462,7 +1438,7 @@
         <v>2</v>
       </c>
       <c r="V11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1512,13 +1488,13 @@
         <v>-400</v>
       </c>
       <c r="Q12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T12">
         <v>1</v>
@@ -1527,7 +1503,7 @@
         <v>3</v>
       </c>
       <c r="V12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1577,13 +1553,13 @@
         <v>-400</v>
       </c>
       <c r="Q13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T13">
         <v>2</v>
@@ -1592,7 +1568,7 @@
         <v>1</v>
       </c>
       <c r="V13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1642,13 +1618,13 @@
         <v>-400</v>
       </c>
       <c r="Q14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T14">
         <v>2</v>
@@ -1657,7 +1633,7 @@
         <v>2</v>
       </c>
       <c r="V14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1707,13 +1683,13 @@
         <v>-400</v>
       </c>
       <c r="Q15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T15">
         <v>2</v>
@@ -1722,7 +1698,7 @@
         <v>3</v>
       </c>
       <c r="V15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1732,500 +1708,557 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>22</v>
       </c>
       <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>55</v>
       </c>
-      <c r="C2">
+      <c r="E2">
         <v>44503</v>
       </c>
-      <c r="D2">
+      <c r="F2">
         <v>1.2</v>
       </c>
-      <c r="E2">
+      <c r="G2">
         <v>2.329800000000032</v>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>9.300000000000001</v>
       </c>
-      <c r="G2">
-        <v>0.000471878300339303</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>22</v>
       </c>
       <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
         <v>56</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>193609</v>
       </c>
-      <c r="D3">
+      <c r="F3">
         <v>1.64</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>2.78</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>10.36</v>
       </c>
-      <c r="G3">
-        <v>0.0002014369166722621</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>22</v>
       </c>
       <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>57</v>
       </c>
-      <c r="C4">
+      <c r="E4">
         <v>129022</v>
       </c>
-      <c r="D4">
+      <c r="F4">
         <v>1.67</v>
       </c>
-      <c r="E4">
+      <c r="G4">
         <v>2.07</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>10.37</v>
       </c>
-      <c r="G4">
-        <v>0.0002557703337415325</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>23</v>
       </c>
       <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
         <v>55</v>
       </c>
-      <c r="C5">
+      <c r="E5">
         <v>44504</v>
       </c>
-      <c r="D5">
+      <c r="F5">
         <v>1.84</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>2.42</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>3.93</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>23</v>
       </c>
       <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
         <v>56</v>
       </c>
-      <c r="C6">
+      <c r="E6">
         <v>193610</v>
       </c>
-      <c r="D6">
+      <c r="F6">
         <v>2.44</v>
       </c>
-      <c r="E6">
+      <c r="G6">
         <v>2.95</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>9.949999999999999</v>
       </c>
-      <c r="G6">
-        <v>0.0003822116626207324</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>23</v>
       </c>
       <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
         <v>57</v>
       </c>
-      <c r="C7">
+      <c r="E7">
         <v>129022</v>
       </c>
-      <c r="D7">
+      <c r="F7">
         <v>2.68</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>3.52</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>10.31</v>
       </c>
-      <c r="G7">
-        <v>9.300739408782998E-05</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>24</v>
       </c>
       <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
         <v>55</v>
       </c>
-      <c r="C8">
+      <c r="E8">
         <v>44501</v>
       </c>
-      <c r="D8">
+      <c r="F8">
         <v>1.58</v>
       </c>
-      <c r="E8">
+      <c r="G8">
         <v>1.89</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>2.92</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>24</v>
       </c>
       <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
         <v>56</v>
       </c>
-      <c r="C9">
+      <c r="E9">
         <v>193610</v>
       </c>
-      <c r="D9">
+      <c r="F9">
         <v>3.36</v>
       </c>
-      <c r="E9">
+      <c r="G9">
         <v>3.83</v>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>8.51</v>
       </c>
-      <c r="G9">
-        <v>1.549506740354321E-05</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>24</v>
       </c>
       <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" t="s">
         <v>57</v>
       </c>
-      <c r="C10">
+      <c r="E10">
         <v>129022</v>
       </c>
-      <c r="D10">
+      <c r="F10">
         <v>3.5</v>
       </c>
-      <c r="E10">
+      <c r="G10">
         <v>4.1</v>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>5.06</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>26</v>
       </c>
       <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
         <v>55</v>
       </c>
-      <c r="C11">
+      <c r="E11">
         <v>44510</v>
       </c>
-      <c r="D11">
+      <c r="F11">
         <v>1.58</v>
       </c>
-      <c r="E11">
+      <c r="G11">
         <v>2.57</v>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>4.46</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>26</v>
       </c>
       <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
         <v>56</v>
       </c>
-      <c r="C12">
+      <c r="E12">
         <v>193600</v>
       </c>
-      <c r="D12">
+      <c r="F12">
         <v>2.13</v>
       </c>
-      <c r="E12">
+      <c r="G12">
         <v>3.48</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>10.32</v>
       </c>
-      <c r="G12">
-        <v>0.0003357438016528926</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>26</v>
       </c>
       <c r="B13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
         <v>57</v>
       </c>
-      <c r="C13">
+      <c r="E13">
         <v>129022</v>
       </c>
-      <c r="D13">
+      <c r="F13">
         <v>1.7</v>
       </c>
-      <c r="E13">
+      <c r="G13">
         <v>2.247899999999936</v>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>10.31</v>
       </c>
-      <c r="G13">
-        <v>0.0002402691013935608</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>27</v>
       </c>
       <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
         <v>55</v>
       </c>
-      <c r="C14">
+      <c r="E14">
         <v>44510</v>
       </c>
-      <c r="D14">
+      <c r="F14">
         <v>1.97</v>
       </c>
-      <c r="E14">
+      <c r="G14">
         <v>2.619099999999962</v>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>3.85</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>27</v>
       </c>
       <c r="B15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15" t="s">
         <v>56</v>
       </c>
-      <c r="C15">
+      <c r="E15">
         <v>193598</v>
       </c>
-      <c r="D15">
+      <c r="F15">
         <v>2.22</v>
       </c>
-      <c r="E15">
+      <c r="G15">
         <v>3.65</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>6.05</v>
       </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>27</v>
       </c>
       <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16" t="s">
         <v>57</v>
       </c>
-      <c r="C16">
+      <c r="E16">
         <v>129022</v>
       </c>
-      <c r="D16">
+      <c r="F16">
         <v>2.2</v>
       </c>
-      <c r="E16">
+      <c r="G16">
         <v>2.79</v>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>3.62</v>
       </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>28</v>
       </c>
       <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17" t="s">
         <v>55</v>
       </c>
-      <c r="C17">
+      <c r="E17">
         <v>44510</v>
       </c>
-      <c r="D17">
+      <c r="F17">
         <v>1.64</v>
       </c>
-      <c r="E17">
+      <c r="G17">
         <v>2.05</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>2.85</v>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>28</v>
       </c>
       <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18" t="s">
         <v>56</v>
       </c>
-      <c r="C18">
+      <c r="E18">
         <v>193610</v>
       </c>
-      <c r="D18">
+      <c r="F18">
         <v>5.08</v>
       </c>
-      <c r="E18">
+      <c r="G18">
         <v>5.54</v>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>10.31</v>
       </c>
-      <c r="G18">
-        <v>0.0006198026961417282</v>
-      </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
         <v>28</v>
       </c>
       <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19" t="s">
         <v>57</v>
       </c>
-      <c r="C19">
+      <c r="E19">
         <v>129022</v>
       </c>
-      <c r="D19">
+      <c r="F19">
         <v>5.01</v>
       </c>
-      <c r="E19">
+      <c r="G19">
         <v>5.48</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>10.31</v>
       </c>
-      <c r="G19">
-        <v>0.0002867727984374758</v>
-      </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2250,10 +2283,10 @@
         <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>59</v>
@@ -2271,7 +2304,7 @@
         <v>63</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>64</v>
@@ -2288,7 +2321,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -2332,7 +2365,7 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -2376,7 +2409,7 @@
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -2420,7 +2453,7 @@
         <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -2464,7 +2497,7 @@
         <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -2508,7 +2541,7 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2552,7 +2585,7 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2596,7 +2629,7 @@
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -2640,7 +2673,7 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -2684,7 +2717,7 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -2728,7 +2761,7 @@
         <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -2772,7 +2805,7 @@
         <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -2816,7 +2849,7 @@
         <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C14">
         <v>3</v>
@@ -2860,7 +2893,7 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -2904,7 +2937,7 @@
         <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -2948,7 +2981,7 @@
         <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -2992,7 +3025,7 @@
         <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -3036,7 +3069,7 @@
         <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -3080,7 +3113,7 @@
         <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -3124,7 +3157,7 @@
         <v>34</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -3168,7 +3201,7 @@
         <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -3212,7 +3245,7 @@
         <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -3256,7 +3289,7 @@
         <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -3300,7 +3333,7 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C25">
         <v>3</v>

--- a/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/validation/D3_operational_envelope_diagnostics.xlsx
+++ b/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/validation/D3_operational_envelope_diagnostics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="121">
   <si>
     <t>sensor_id</t>
   </si>
@@ -826,19 +826,19 @@
         <v>0.004231770833333333</v>
       </c>
       <c r="D2">
-        <v>0.02571614583333333</v>
+        <v>0.02766927083333333</v>
       </c>
       <c r="E2">
         <v>9.156512909776618E-05</v>
       </c>
       <c r="F2">
-        <v>0.008047758920800696</v>
+        <v>0.008297976501305484</v>
       </c>
       <c r="G2">
         <v>0.02</v>
       </c>
       <c r="H2">
-        <v>7.881522987720899</v>
+        <v>7.927034085789853</v>
       </c>
       <c r="I2">
         <v>0.004231770833333333</v>
@@ -888,19 +888,19 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>0.0615234375</v>
+        <v>0.06673177083333333</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0.01225794168842472</v>
+        <v>0.01285628807658834</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>7.277511266220876</v>
+        <v>7.291502311270616</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -950,19 +950,19 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>0.003255208333333333</v>
+        <v>0.0029296875</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.0009818320278503045</v>
+        <v>0.0007968885987815492</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>4.379834524927852</v>
+        <v>4.197219083227807</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1074,19 +1074,19 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0.04720052083333334</v>
+        <v>0.05110677083333334</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.01921030161411823</v>
+        <v>0.02062729465154208</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7.634317837507574</v>
+        <v>7.692245192185338</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1136,19 +1136,19 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0.03776041666666666</v>
+        <v>0.03841145833333334</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0.01685515263546672</v>
+        <v>0.01709993070335184</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>2.8541182515103</v>
+        <v>2.886189252768078</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1198,19 +1198,19 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0.5335286458333334</v>
+        <v>0.4508463541666667</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0.08725617790361966</v>
+        <v>0.05474846459088568</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>5.724192996097323</v>
+        <v>5.534821397557533</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -2269,7 +2269,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -2318,37 +2318,37 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
         <v>55</v>
       </c>
       <c r="E2">
-        <v>44503</v>
+        <v>44505</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>-223.03</v>
       </c>
       <c r="G2">
-        <v>0.014826</v>
+        <v>26.62749600000001</v>
       </c>
       <c r="H2">
-        <v>-0.044478</v>
+        <v>-302.9124880000001</v>
       </c>
       <c r="I2">
-        <v>0.044478</v>
+        <v>-143.1475119999999</v>
       </c>
       <c r="J2">
-        <v>-0.02</v>
+        <v>-264.2684</v>
       </c>
       <c r="K2">
-        <v>0.48</v>
+        <v>-153.7316</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -2362,37 +2362,37 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3" t="s">
         <v>56</v>
       </c>
       <c r="E3">
-        <v>193597</v>
+        <v>193615</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>-199.93</v>
       </c>
       <c r="G3">
-        <v>0.014826</v>
+        <v>66.86525999999999</v>
       </c>
       <c r="H3">
-        <v>-0.044478</v>
+        <v>-400.52578</v>
       </c>
       <c r="I3">
-        <v>0.044478</v>
+        <v>0.6657799999999838</v>
       </c>
       <c r="J3">
-        <v>-0.02</v>
+        <v>-303.2172</v>
       </c>
       <c r="K3">
-        <v>0.46</v>
+        <v>-61.60280000000028</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -2406,37 +2406,37 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4" t="s">
         <v>57</v>
       </c>
       <c r="E4">
-        <v>129021</v>
+        <v>129022</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>-241.825</v>
       </c>
       <c r="G4">
-        <v>0.014826</v>
+        <v>26.32356299999999</v>
       </c>
       <c r="H4">
-        <v>-0.044478</v>
+        <v>-320.795689</v>
       </c>
       <c r="I4">
-        <v>0.044478</v>
+        <v>-162.854311</v>
       </c>
       <c r="J4">
-        <v>-0.02</v>
+        <v>-288.8779</v>
       </c>
       <c r="K4">
-        <v>0.28</v>
+        <v>-134.97</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -2450,37 +2450,37 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5" t="s">
         <v>55</v>
       </c>
       <c r="E5">
-        <v>44510</v>
+        <v>44504</v>
       </c>
       <c r="F5">
-        <v>0.13</v>
+        <v>-213.2</v>
       </c>
       <c r="G5">
-        <v>0.133434</v>
+        <v>42.80266200000001</v>
       </c>
       <c r="H5">
-        <v>-0.270302</v>
+        <v>-341.607986</v>
       </c>
       <c r="I5">
-        <v>0.5303020000000001</v>
+        <v>-84.79201399999997</v>
       </c>
       <c r="J5">
-        <v>0.01</v>
+        <v>-271.2494</v>
       </c>
       <c r="K5">
-        <v>1.02</v>
+        <v>-108.9014999999999</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -2494,40 +2494,40 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
       </c>
       <c r="E6">
-        <v>193598</v>
+        <v>193611</v>
       </c>
       <c r="F6">
-        <v>0.15</v>
+        <v>-147.97</v>
       </c>
       <c r="G6">
-        <v>0.14826</v>
+        <v>66.82078199999998</v>
       </c>
       <c r="H6">
-        <v>-0.2947799999999999</v>
+        <v>-348.4323459999999</v>
       </c>
       <c r="I6">
-        <v>0.59478</v>
+        <v>52.49234599999994</v>
       </c>
       <c r="J6">
-        <v>0.02</v>
+        <v>-396.768</v>
       </c>
       <c r="K6">
-        <v>2.32</v>
+        <v>-42.67</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>0.006791969464544886</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -2538,13 +2538,13 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" t="s">
         <v>57</v>
@@ -2553,25 +2553,25 @@
         <v>129022</v>
       </c>
       <c r="F7">
-        <v>0.07000000000000001</v>
+        <v>-172.23</v>
       </c>
       <c r="G7">
-        <v>0.029652</v>
+        <v>67.13212799999998</v>
       </c>
       <c r="H7">
-        <v>-0.018956</v>
+        <v>-373.6263839999999</v>
       </c>
       <c r="I7">
-        <v>0.158956</v>
+        <v>29.16638399999997</v>
       </c>
       <c r="J7">
-        <v>0.03</v>
+        <v>-404.93</v>
       </c>
       <c r="K7">
-        <v>2.4</v>
+        <v>-88.73</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>0.01989583171862163</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -2582,40 +2582,40 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="s">
         <v>55</v>
       </c>
       <c r="E8">
-        <v>44505</v>
+        <v>44504</v>
       </c>
       <c r="F8">
-        <v>-223.03</v>
+        <v>-265.2</v>
       </c>
       <c r="G8">
-        <v>26.62749600000001</v>
+        <v>98.44464000000001</v>
       </c>
       <c r="H8">
-        <v>-302.9124880000001</v>
+        <v>-560.5339200000001</v>
       </c>
       <c r="I8">
-        <v>-143.1475119999999</v>
+        <v>30.13392000000005</v>
       </c>
       <c r="J8">
-        <v>-264.2684</v>
+        <v>-487.1688</v>
       </c>
       <c r="K8">
-        <v>-153.7316</v>
+        <v>-95.8</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>0.1310668703936725</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -2626,40 +2626,40 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
       </c>
       <c r="E9">
-        <v>193615</v>
+        <v>193612</v>
       </c>
       <c r="F9">
-        <v>-199.93</v>
+        <v>-147.83</v>
       </c>
       <c r="G9">
-        <v>66.86525999999999</v>
+        <v>163.723518</v>
       </c>
       <c r="H9">
-        <v>-400.52578</v>
+        <v>-639.0005540000001</v>
       </c>
       <c r="I9">
-        <v>0.6657799999999838</v>
+        <v>343.340554</v>
       </c>
       <c r="J9">
-        <v>-303.2172</v>
+        <v>-499.5</v>
       </c>
       <c r="K9">
-        <v>-61.60280000000028</v>
+        <v>23.95</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>0.1573404541040845</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -2670,13 +2670,13 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -2685,25 +2685,25 @@
         <v>129022</v>
       </c>
       <c r="F10">
-        <v>-241.825</v>
+        <v>-194.07</v>
       </c>
       <c r="G10">
-        <v>26.32356299999999</v>
+        <v>66.27222000000002</v>
       </c>
       <c r="H10">
-        <v>-320.795689</v>
+        <v>-392.8866600000001</v>
       </c>
       <c r="I10">
-        <v>-162.854311</v>
+        <v>4.746660000000077</v>
       </c>
       <c r="J10">
-        <v>-288.8779</v>
+        <v>-491.8779</v>
       </c>
       <c r="K10">
-        <v>-134.97</v>
+        <v>-19.68420000000013</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>0.1546635457518873</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -2714,37 +2714,37 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="s">
         <v>55</v>
       </c>
       <c r="E11">
-        <v>44504</v>
+        <v>44509</v>
       </c>
       <c r="F11">
-        <v>-213.2</v>
+        <v>-247.88</v>
       </c>
       <c r="G11">
-        <v>42.80266200000001</v>
+        <v>23.84020799999998</v>
       </c>
       <c r="H11">
-        <v>-341.607986</v>
+        <v>-319.4006239999999</v>
       </c>
       <c r="I11">
-        <v>-84.79201399999997</v>
+        <v>-176.3593760000001</v>
       </c>
       <c r="J11">
-        <v>-271.2494</v>
+        <v>-284.1484</v>
       </c>
       <c r="K11">
-        <v>-108.9014999999999</v>
+        <v>-159.8080000000002</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -2758,40 +2758,40 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="s">
         <v>56</v>
       </c>
       <c r="E12">
-        <v>193611</v>
+        <v>193607</v>
       </c>
       <c r="F12">
-        <v>-147.97</v>
+        <v>-198.4</v>
       </c>
       <c r="G12">
-        <v>66.82078199999998</v>
+        <v>53.96664000000001</v>
       </c>
       <c r="H12">
-        <v>-348.4323459999999</v>
+        <v>-360.29992</v>
       </c>
       <c r="I12">
-        <v>52.49234599999994</v>
+        <v>-36.50008</v>
       </c>
       <c r="J12">
-        <v>-396.768</v>
+        <v>-380.63</v>
       </c>
       <c r="K12">
-        <v>-42.67</v>
+        <v>-5.770599999999976</v>
       </c>
       <c r="L12">
-        <v>0.006791969464544886</v>
+        <v>0</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -2802,13 +2802,13 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="s">
         <v>57</v>
@@ -2817,25 +2817,25 @@
         <v>129022</v>
       </c>
       <c r="F13">
-        <v>-172.23</v>
+        <v>-214.3</v>
       </c>
       <c r="G13">
-        <v>67.13212799999998</v>
+        <v>31.920378</v>
       </c>
       <c r="H13">
-        <v>-373.6263839999999</v>
+        <v>-310.061134</v>
       </c>
       <c r="I13">
-        <v>29.16638399999997</v>
+        <v>-118.538866</v>
       </c>
       <c r="J13">
-        <v>-404.93</v>
+        <v>-261.4</v>
       </c>
       <c r="K13">
-        <v>-88.73</v>
+        <v>-91.65420000000013</v>
       </c>
       <c r="L13">
-        <v>0.01989583171862163</v>
+        <v>0</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -2846,40 +2846,40 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="s">
         <v>55</v>
       </c>
       <c r="E14">
-        <v>44504</v>
+        <v>44508</v>
       </c>
       <c r="F14">
-        <v>-265.2</v>
+        <v>-336.2</v>
       </c>
       <c r="G14">
-        <v>98.44464000000001</v>
+        <v>29.05895999999995</v>
       </c>
       <c r="H14">
-        <v>-560.5339200000001</v>
+        <v>-423.3768799999998</v>
       </c>
       <c r="I14">
-        <v>30.13392000000005</v>
+        <v>-249.0231200000001</v>
       </c>
       <c r="J14">
-        <v>-487.1688</v>
+        <v>-371.1986</v>
       </c>
       <c r="K14">
-        <v>-95.8</v>
+        <v>-285.4207</v>
       </c>
       <c r="L14">
-        <v>0.1310668703936725</v>
+        <v>0</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -2890,40 +2890,40 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="s">
         <v>56</v>
       </c>
       <c r="E15">
-        <v>193612</v>
+        <v>193607</v>
       </c>
       <c r="F15">
-        <v>-147.83</v>
+        <v>-280.82</v>
       </c>
       <c r="G15">
-        <v>163.723518</v>
+        <v>25.87136999999998</v>
       </c>
       <c r="H15">
-        <v>-639.0005540000001</v>
+        <v>-358.4341099999999</v>
       </c>
       <c r="I15">
-        <v>343.340554</v>
+        <v>-203.2058900000001</v>
       </c>
       <c r="J15">
-        <v>-499.5</v>
+        <v>-391.65</v>
       </c>
       <c r="K15">
-        <v>23.95</v>
+        <v>-224</v>
       </c>
       <c r="L15">
-        <v>0.1573404541040845</v>
+        <v>0.001296440727866245</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -2934,13 +2934,13 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="s">
         <v>57</v>
@@ -2949,25 +2949,25 @@
         <v>129022</v>
       </c>
       <c r="F16">
-        <v>-194.07</v>
+        <v>-283.2</v>
       </c>
       <c r="G16">
-        <v>66.27222000000002</v>
+        <v>29.20721999999998</v>
       </c>
       <c r="H16">
-        <v>-392.8866600000001</v>
+        <v>-370.82166</v>
       </c>
       <c r="I16">
-        <v>4.746660000000077</v>
+        <v>-195.57834</v>
       </c>
       <c r="J16">
-        <v>-491.8779</v>
+        <v>-385.67</v>
       </c>
       <c r="K16">
-        <v>-19.68420000000013</v>
+        <v>-244.58</v>
       </c>
       <c r="L16">
-        <v>0.1546635457518873</v>
+        <v>0</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -2978,40 +2978,40 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" t="s">
         <v>55</v>
       </c>
       <c r="E17">
-        <v>44509</v>
+        <v>44510</v>
       </c>
       <c r="F17">
-        <v>-247.88</v>
+        <v>-373.93</v>
       </c>
       <c r="G17">
-        <v>23.84020799999998</v>
+        <v>138.652752</v>
       </c>
       <c r="H17">
-        <v>-319.4006239999999</v>
+        <v>-789.888256</v>
       </c>
       <c r="I17">
-        <v>-176.3593760000001</v>
+        <v>42.02825599999989</v>
       </c>
       <c r="J17">
-        <v>-284.1484</v>
+        <v>-481.55</v>
       </c>
       <c r="K17">
-        <v>-159.8080000000002</v>
+        <v>-3.520900000000038</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>0.4344866322174792</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -3022,40 +3022,40 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" t="s">
         <v>56</v>
       </c>
       <c r="E18">
-        <v>193607</v>
+        <v>193608</v>
       </c>
       <c r="F18">
-        <v>-198.4</v>
+        <v>-386.525</v>
       </c>
       <c r="G18">
-        <v>53.96664000000001</v>
+        <v>115.798473</v>
       </c>
       <c r="H18">
-        <v>-360.29992</v>
+        <v>-733.920419</v>
       </c>
       <c r="I18">
-        <v>-36.50008</v>
+        <v>-39.12958099999992</v>
       </c>
       <c r="J18">
-        <v>-380.63</v>
+        <v>-478.3</v>
       </c>
       <c r="K18">
-        <v>-5.770599999999976</v>
+        <v>38.5</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>0.4748874013470518</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -3066,13 +3066,13 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" t="s">
         <v>57</v>
@@ -3081,294 +3081,30 @@
         <v>129022</v>
       </c>
       <c r="F19">
-        <v>-214.3</v>
+        <v>-449.6</v>
       </c>
       <c r="G19">
-        <v>31.920378</v>
+        <v>6.968220000000067</v>
       </c>
       <c r="H19">
-        <v>-310.061134</v>
+        <v>-470.5046600000002</v>
       </c>
       <c r="I19">
-        <v>-118.538866</v>
+        <v>-428.6953399999998</v>
       </c>
       <c r="J19">
-        <v>-261.4</v>
+        <v>-460.3958</v>
       </c>
       <c r="K19">
-        <v>-91.65420000000013</v>
+        <v>-218.6063000000002</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>0.8886003937313016</v>
       </c>
       <c r="M19">
         <v>0</v>
       </c>
       <c r="N19" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20">
-        <v>2</v>
-      </c>
-      <c r="D20" t="s">
-        <v>55</v>
-      </c>
-      <c r="E20">
-        <v>44508</v>
-      </c>
-      <c r="F20">
-        <v>-336.2</v>
-      </c>
-      <c r="G20">
-        <v>29.05895999999995</v>
-      </c>
-      <c r="H20">
-        <v>-423.3768799999998</v>
-      </c>
-      <c r="I20">
-        <v>-249.0231200000001</v>
-      </c>
-      <c r="J20">
-        <v>-371.1986</v>
-      </c>
-      <c r="K20">
-        <v>-285.4207</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21">
-        <v>2</v>
-      </c>
-      <c r="D21" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21">
-        <v>193607</v>
-      </c>
-      <c r="F21">
-        <v>-280.82</v>
-      </c>
-      <c r="G21">
-        <v>25.87136999999998</v>
-      </c>
-      <c r="H21">
-        <v>-358.4341099999999</v>
-      </c>
-      <c r="I21">
-        <v>-203.2058900000001</v>
-      </c>
-      <c r="J21">
-        <v>-391.65</v>
-      </c>
-      <c r="K21">
-        <v>-224</v>
-      </c>
-      <c r="L21">
-        <v>0.001296440727866245</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="A22" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22">
-        <v>2</v>
-      </c>
-      <c r="D22" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22">
-        <v>129022</v>
-      </c>
-      <c r="F22">
-        <v>-283.2</v>
-      </c>
-      <c r="G22">
-        <v>29.20721999999998</v>
-      </c>
-      <c r="H22">
-        <v>-370.82166</v>
-      </c>
-      <c r="I22">
-        <v>-195.57834</v>
-      </c>
-      <c r="J22">
-        <v>-385.67</v>
-      </c>
-      <c r="K22">
-        <v>-244.58</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23">
-        <v>3</v>
-      </c>
-      <c r="D23" t="s">
-        <v>55</v>
-      </c>
-      <c r="E23">
-        <v>44510</v>
-      </c>
-      <c r="F23">
-        <v>-373.93</v>
-      </c>
-      <c r="G23">
-        <v>138.652752</v>
-      </c>
-      <c r="H23">
-        <v>-789.888256</v>
-      </c>
-      <c r="I23">
-        <v>42.02825599999989</v>
-      </c>
-      <c r="J23">
-        <v>-481.55</v>
-      </c>
-      <c r="K23">
-        <v>-3.520900000000038</v>
-      </c>
-      <c r="L23">
-        <v>0.4344866322174792</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24">
-        <v>3</v>
-      </c>
-      <c r="D24" t="s">
-        <v>56</v>
-      </c>
-      <c r="E24">
-        <v>193608</v>
-      </c>
-      <c r="F24">
-        <v>-386.525</v>
-      </c>
-      <c r="G24">
-        <v>115.798473</v>
-      </c>
-      <c r="H24">
-        <v>-733.920419</v>
-      </c>
-      <c r="I24">
-        <v>-39.12958099999992</v>
-      </c>
-      <c r="J24">
-        <v>-478.3</v>
-      </c>
-      <c r="K24">
-        <v>38.5</v>
-      </c>
-      <c r="L24">
-        <v>0.4748874013470518</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25">
-        <v>3</v>
-      </c>
-      <c r="D25" t="s">
-        <v>57</v>
-      </c>
-      <c r="E25">
-        <v>129022</v>
-      </c>
-      <c r="F25">
-        <v>-449.6</v>
-      </c>
-      <c r="G25">
-        <v>6.968220000000067</v>
-      </c>
-      <c r="H25">
-        <v>-470.5046600000002</v>
-      </c>
-      <c r="I25">
-        <v>-428.6953399999998</v>
-      </c>
-      <c r="J25">
-        <v>-460.3958</v>
-      </c>
-      <c r="K25">
-        <v>-218.6063000000002</v>
-      </c>
-      <c r="L25">
-        <v>0.8886003937313016</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25" t="s">
         <v>67</v>
       </c>
     </row>

--- a/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/validation/D3_operational_envelope_diagnostics.xlsx
+++ b/Project 1 Data Quality Assessment/D3 Physical rationality and rate constraints/outputs/validation/D3_operational_envelope_diagnostics.xlsx
@@ -13,14 +13,16 @@
     <sheet name="DO4_zero_eq_sensitivity" sheetId="4" r:id="rId4"/>
     <sheet name="DO4_monthly_zero_stability" sheetId="5" r:id="rId5"/>
     <sheet name="DO4_parallel_line_diagnostic" sheetId="6" r:id="rId6"/>
-    <sheet name="DO4_upper_candidate" sheetId="7" r:id="rId7"/>
+    <sheet name="ORP_position_distribution" sheetId="7" r:id="rId7"/>
+    <sheet name="ORP_parallel_position_effect" sheetId="8" r:id="rId8"/>
+    <sheet name="DO4_upper_candidate" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="141">
   <si>
     <t>sensor_id</t>
   </si>
@@ -304,6 +306,21 @@
     <t>DO_2_4_median</t>
   </si>
   <si>
+    <t>paired_delta_median_mg_L</t>
+  </si>
+  <si>
+    <t>paired_delta_day_block_ci_low</t>
+  </si>
+  <si>
+    <t>paired_delta_day_block_ci_high</t>
+  </si>
+  <si>
+    <t>paired_delta_n_days</t>
+  </si>
+  <si>
+    <t>paired_robust_standardized_difference</t>
+  </si>
+  <si>
     <t>negative_jaccard</t>
   </si>
   <si>
@@ -320,6 +337,51 @@
   </si>
   <si>
     <t>parallel_line_diagnostic_not_cross_sensor_scoring</t>
+  </si>
+  <si>
+    <t>p01_mV</t>
+  </si>
+  <si>
+    <t>q25_mV</t>
+  </si>
+  <si>
+    <t>median_mV</t>
+  </si>
+  <si>
+    <t>q75_mV</t>
+  </si>
+  <si>
+    <t>p99_mV</t>
+  </si>
+  <si>
+    <t>full_period_distribution_context_not_scoring_template</t>
+  </si>
+  <si>
+    <t>line_1_sensor</t>
+  </si>
+  <si>
+    <t>line_2_sensor</t>
+  </si>
+  <si>
+    <t>n_paired_minutes</t>
+  </si>
+  <si>
+    <t>n_day_blocks</t>
+  </si>
+  <si>
+    <t>median_line1_minus_line2_mV</t>
+  </si>
+  <si>
+    <t>day_block_ci_low_mV</t>
+  </si>
+  <si>
+    <t>day_block_ci_high_mV</t>
+  </si>
+  <si>
+    <t>robust_standardized_difference</t>
+  </si>
+  <si>
+    <t>parallel_line_heterogeneity_diagnostic_not_scoring_template</t>
   </si>
   <si>
     <t>split_timestamp</t>
@@ -3983,10 +4045,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>75</v>
       </c>
@@ -4014,8 +4076,23 @@
       <c r="I1" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>82</v>
       </c>
@@ -4029,22 +4106,37 @@
         <v>0.13</v>
       </c>
       <c r="E2">
+        <v>-0.12</v>
+      </c>
+      <c r="F2">
+        <v>-0.14</v>
+      </c>
+      <c r="G2">
+        <v>-0.1</v>
+      </c>
+      <c r="H2">
+        <v>31</v>
+      </c>
+      <c r="I2">
+        <v>-1.264053111198754</v>
+      </c>
+      <c r="J2">
         <v>0.0002117746717492588</v>
       </c>
-      <c r="F2">
+      <c r="K2">
         <v>0.0002117746717492588</v>
       </c>
-      <c r="G2">
+      <c r="L2">
         <v>0.3182165490583846</v>
       </c>
-      <c r="H2">
+      <c r="M2">
         <v>0.0002022562811811767</v>
       </c>
-      <c r="I2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="N2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>83</v>
       </c>
@@ -4058,22 +4150,37 @@
         <v>0.3</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>-0.49</v>
       </c>
       <c r="G3">
+        <v>-0.22</v>
+      </c>
+      <c r="H3">
+        <v>30</v>
+      </c>
+      <c r="I3">
+        <v>-1.243009139688287</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
         <v>0.3292785430772823</v>
       </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>84</v>
       </c>
@@ -4087,22 +4194,37 @@
         <v>0.16</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="G4">
+        <v>-0.1</v>
+      </c>
+      <c r="H4">
+        <v>31</v>
+      </c>
+      <c r="I4">
+        <v>-1.029793990785262</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
         <v>0.2186610484792792</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>85</v>
       </c>
@@ -4116,22 +4238,37 @@
         <v>0.21</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="G5">
+        <v>-0.125</v>
+      </c>
+      <c r="H5">
+        <v>30</v>
+      </c>
+      <c r="I5">
+        <v>-1.332935288442552</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
         <v>0.2064892656152296</v>
       </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>86</v>
       </c>
@@ -4145,22 +4282,37 @@
         <v>0.06</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>-0.06999999999999999</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>-0.06999999999999999</v>
       </c>
       <c r="G6">
+        <v>-0.06</v>
+      </c>
+      <c r="H6">
+        <v>31</v>
+      </c>
+      <c r="I6">
+        <v>-2.986097884955977</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
         <v>0.3059811827956989</v>
       </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>87</v>
       </c>
@@ -4174,22 +4326,37 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>-0.06999999999999999</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G7">
+        <v>-0.06</v>
+      </c>
+      <c r="H7">
+        <v>31</v>
+      </c>
+      <c r="I7">
+        <v>-2.986097884955976</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
         <v>0.2220330904881868</v>
       </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>88</v>
       </c>
@@ -4203,22 +4370,37 @@
         <v>0.08</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="G8">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="H8">
+        <v>28</v>
+      </c>
+      <c r="I8">
+        <v>-2.413131501416204</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
         <v>0.2364831349206349</v>
       </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>89</v>
       </c>
@@ -4232,22 +4414,37 @@
         <v>0.09</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="G9">
+        <v>-0.08</v>
+      </c>
+      <c r="H9">
+        <v>31</v>
+      </c>
+      <c r="I9">
+        <v>-1.850787375070917</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
         <v>0.1788306451612903</v>
       </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
         <v>90</v>
       </c>
@@ -4261,19 +4458,34 @@
         <v>0.05</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G10">
+        <v>-0.05</v>
+      </c>
+      <c r="H10">
+        <v>13</v>
+      </c>
+      <c r="I10">
+        <v>-3.372453797382976</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
         <v>0.2748116606616443</v>
       </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10" t="s">
-        <v>99</v>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -4283,6 +4495,378 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>367142</v>
+      </c>
+      <c r="E2">
+        <v>-299.07</v>
+      </c>
+      <c r="F2">
+        <v>-258.27</v>
+      </c>
+      <c r="G2">
+        <v>-226.47</v>
+      </c>
+      <c r="H2">
+        <v>-188.07</v>
+      </c>
+      <c r="I2">
+        <v>-74.4081999999995</v>
+      </c>
+      <c r="J2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>367138</v>
+      </c>
+      <c r="E3">
+        <v>-374.23</v>
+      </c>
+      <c r="F3">
+        <v>-236.78</v>
+      </c>
+      <c r="G3">
+        <v>-211.67</v>
+      </c>
+      <c r="H3">
+        <v>-174.53</v>
+      </c>
+      <c r="I3">
+        <v>-16.6</v>
+      </c>
+      <c r="J3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>367137</v>
+      </c>
+      <c r="E4">
+        <v>-400.37</v>
+      </c>
+      <c r="F4">
+        <v>-237.77</v>
+      </c>
+      <c r="G4">
+        <v>-163.7</v>
+      </c>
+      <c r="H4">
+        <v>-127.63</v>
+      </c>
+      <c r="I4">
+        <v>-51.5</v>
+      </c>
+      <c r="J4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>367137</v>
+      </c>
+      <c r="E5">
+        <v>-388</v>
+      </c>
+      <c r="F5">
+        <v>-326.73</v>
+      </c>
+      <c r="G5">
+        <v>-286.87</v>
+      </c>
+      <c r="H5">
+        <v>-269.97</v>
+      </c>
+      <c r="I5">
+        <v>-226.65</v>
+      </c>
+      <c r="J5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>367138</v>
+      </c>
+      <c r="E6">
+        <v>-494.33</v>
+      </c>
+      <c r="F6">
+        <v>-291.13</v>
+      </c>
+      <c r="G6">
+        <v>-188.17</v>
+      </c>
+      <c r="H6">
+        <v>-111.9</v>
+      </c>
+      <c r="I6">
+        <v>17.63</v>
+      </c>
+      <c r="J6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>367140</v>
+      </c>
+      <c r="E7">
+        <v>-477.5</v>
+      </c>
+      <c r="F7">
+        <v>-451.87</v>
+      </c>
+      <c r="G7">
+        <v>-431.87</v>
+      </c>
+      <c r="H7">
+        <v>-206.03</v>
+      </c>
+      <c r="I7">
+        <v>32.9</v>
+      </c>
+      <c r="J7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2">
+        <v>367126</v>
+      </c>
+      <c r="E2">
+        <v>256</v>
+      </c>
+      <c r="F2">
+        <v>-21.06999999999999</v>
+      </c>
+      <c r="G2">
+        <v>-28.52249999999999</v>
+      </c>
+      <c r="H2">
+        <v>-12.0135625</v>
+      </c>
+      <c r="I2">
+        <v>-0.4445668259970538</v>
+      </c>
+      <c r="J2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3">
+        <v>367123</v>
+      </c>
+      <c r="E3">
+        <v>256</v>
+      </c>
+      <c r="F3">
+        <v>125.86</v>
+      </c>
+      <c r="G3">
+        <v>122.046875</v>
+      </c>
+      <c r="H3">
+        <v>131.33075</v>
+      </c>
+      <c r="I3">
+        <v>2.202783325808403</v>
+      </c>
+      <c r="J3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4">
+        <v>367127</v>
+      </c>
+      <c r="E4">
+        <v>256</v>
+      </c>
+      <c r="F4">
+        <v>201.26</v>
+      </c>
+      <c r="G4">
+        <v>151.34375</v>
+      </c>
+      <c r="H4">
+        <v>236.080625</v>
+      </c>
+      <c r="I4">
+        <v>2.102465560258462</v>
+      </c>
+      <c r="J4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -4291,49 +4875,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -4371,19 +4955,19 @@
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="M2" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="N2" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="O2" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="P2" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -4421,19 +5005,19 @@
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="M3" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="N3" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="O3" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="P3" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
